--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -2228,10 +2228,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118022407</v>
+        <v>118022366</v>
       </c>
       <c r="B15" t="n">
-        <v>102044</v>
+        <v>108703</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2240,52 +2240,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701353</v>
+        <v>701112</v>
       </c>
       <c r="R15" t="n">
-        <v>6359389</v>
+        <v>6359275</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2318,11 +2304,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>30 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2354,10 +2335,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118022366</v>
+        <v>118022407</v>
       </c>
       <c r="B16" t="n">
-        <v>108703</v>
+        <v>102044</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,38 +2347,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701112</v>
+        <v>701353</v>
       </c>
       <c r="R16" t="n">
-        <v>6359275</v>
+        <v>6359389</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2430,6 +2425,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>30 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118022427</v>
+        <v>118022538</v>
       </c>
       <c r="B2" t="n">
-        <v>100097</v>
+        <v>57990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701333</v>
+        <v>701298</v>
       </c>
       <c r="R2" t="n">
-        <v>6359501</v>
+        <v>6359287</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,11 +770,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118022399</v>
+        <v>118022427</v>
       </c>
       <c r="B3" t="n">
-        <v>102044</v>
+        <v>100097</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,55 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6037533</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701351</v>
+        <v>701333</v>
       </c>
       <c r="R3" t="n">
-        <v>6359353</v>
+        <v>6359501</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,11 +864,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mindre plantor.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -890,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118022395</v>
+        <v>118022475</v>
       </c>
       <c r="B4" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,12 +933,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701356</v>
+        <v>701355</v>
       </c>
       <c r="R4" t="n">
-        <v>6359344</v>
+        <v>6359352</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,23 +990,19 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 m hög.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118022401</v>
+        <v>118022348</v>
       </c>
       <c r="B5" t="n">
         <v>102044</v>
@@ -1088,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701357</v>
+        <v>701238</v>
       </c>
       <c r="R5" t="n">
-        <v>6359355</v>
+        <v>6359519</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1128,7 +1114,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ca 3 m hög, stam 5 cm i diameter, fertil, död stam 4 cm med skott.</t>
+          <t>1,2 m hög.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1128,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1160,7 +1146,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118022404</v>
+        <v>118022408</v>
       </c>
       <c r="B6" t="n">
         <v>102044</v>
@@ -1195,7 +1181,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1214,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701354</v>
+        <v>701358</v>
       </c>
       <c r="R6" t="n">
-        <v>6359377</v>
+        <v>6359389</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4-5 m höga, spensliga, sterila =angripna.</t>
+          <t>40 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1286,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118022371</v>
+        <v>118022399</v>
       </c>
       <c r="B7" t="n">
-        <v>106109</v>
+        <v>102044</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,41 +1284,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221849</v>
+        <v>6037533</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701190</v>
+        <v>701351</v>
       </c>
       <c r="R7" t="n">
-        <v>6359305</v>
+        <v>6359353</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Tycks spridd l'ängs rävstig.</t>
+          <t>Mindre plantor.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar; gammalt grustag i strandvall ev.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118022473</v>
+        <v>118022405</v>
       </c>
       <c r="B8" t="n">
-        <v>42953</v>
+        <v>106765</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,41 +1414,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101242</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1457,13 +1452,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701221</v>
+        <v>701354</v>
       </c>
       <c r="R8" t="n">
-        <v>6359309</v>
+        <v>6359384</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1501,13 +1496,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1525,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118022398</v>
+        <v>118022369</v>
       </c>
       <c r="B9" t="n">
-        <v>102044</v>
+        <v>108703</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,55 +1531,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701355</v>
+        <v>701176</v>
       </c>
       <c r="R9" t="n">
-        <v>6359352</v>
+        <v>6359312</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1617,11 +1597,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>60 cm hög.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1633,7 +1608,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1651,7 +1626,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118022408</v>
+        <v>118022404</v>
       </c>
       <c r="B10" t="n">
         <v>102044</v>
@@ -1686,7 +1661,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1705,13 +1680,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701358</v>
+        <v>701354</v>
       </c>
       <c r="R10" t="n">
-        <v>6359389</v>
+        <v>6359377</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1745,7 +1720,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>40 cm hög. Flackare strandvall.</t>
+          <t>4-5 m höga, spensliga, sterila =angripna.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1734,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1777,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118022540</v>
+        <v>118022371</v>
       </c>
       <c r="B11" t="n">
-        <v>57303</v>
+        <v>106109</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1793,46 +1768,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701365</v>
+        <v>701190</v>
       </c>
       <c r="R11" t="n">
-        <v>6359342</v>
+        <v>6359305</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1864,6 +1830,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tycks spridd l'ängs rävstig.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1872,6 +1843,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalktallskog med mycket enbuskar; gammalt grustag i strandvall ev.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1888,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118022384</v>
+        <v>118022396</v>
       </c>
       <c r="B12" t="n">
-        <v>108703</v>
+        <v>102044</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1900,41 +1876,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701278</v>
+        <v>701356</v>
       </c>
       <c r="R12" t="n">
-        <v>6359306</v>
+        <v>6359346</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,6 +1956,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>80 cm hög.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1977,7 +1972,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1995,10 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118022394</v>
+        <v>118022402</v>
       </c>
       <c r="B13" t="n">
-        <v>108703</v>
+        <v>102044</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,41 +2002,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701358</v>
+        <v>701357</v>
       </c>
       <c r="R13" t="n">
-        <v>6359325</v>
+        <v>6359376</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2073,6 +2082,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,5 m (steril, angripen) + 4 m höga (fertil).</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2084,7 +2098,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2102,7 +2116,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118022348</v>
+        <v>118022401</v>
       </c>
       <c r="B14" t="n">
         <v>102044</v>
@@ -2156,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701238</v>
+        <v>701357</v>
       </c>
       <c r="R14" t="n">
-        <v>6359519</v>
+        <v>6359355</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2196,7 +2210,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1,2 m hög.</t>
+          <t>ca 3 m hög, stam 5 cm i diameter, fertil, död stam 4 cm med skott.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,7 +2224,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2228,10 +2242,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118022366</v>
+        <v>118022474</v>
       </c>
       <c r="B15" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2244,37 +2258,56 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701112</v>
+        <v>701336</v>
       </c>
       <c r="R15" t="n">
-        <v>6359275</v>
+        <v>6359312</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2312,12 +2345,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2335,10 +2369,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118022407</v>
+        <v>118022473</v>
       </c>
       <c r="B16" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,40 +2381,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2389,13 +2428,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701353</v>
+        <v>701221</v>
       </c>
       <c r="R16" t="n">
-        <v>6359389</v>
+        <v>6359309</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2427,23 +2466,19 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>30 cm hög. Flackare strandvall.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2461,10 +2496,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118022346</v>
+        <v>118022366</v>
       </c>
       <c r="B17" t="n">
-        <v>102044</v>
+        <v>108703</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,55 +2508,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701238</v>
+        <v>701112</v>
       </c>
       <c r="R17" t="n">
-        <v>6359528</v>
+        <v>6359275</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2551,11 +2572,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1,1 m hög.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2587,7 +2603,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118022376</v>
+        <v>118022398</v>
       </c>
       <c r="B18" t="n">
         <v>102044</v>
@@ -2641,13 +2657,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701237</v>
+        <v>701355</v>
       </c>
       <c r="R18" t="n">
-        <v>6359313</v>
+        <v>6359352</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2681,7 +2697,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1m hög; på åsrygg.</t>
+          <t>60 cm hög.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2695,7 +2711,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2713,7 +2729,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118022388</v>
+        <v>118022384</v>
       </c>
       <c r="B19" t="n">
         <v>108703</v>
@@ -2753,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701297</v>
+        <v>701278</v>
       </c>
       <c r="R19" t="n">
-        <v>6359321</v>
+        <v>6359306</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2820,10 +2836,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118022405</v>
+        <v>118022540</v>
       </c>
       <c r="B20" t="n">
-        <v>106765</v>
+        <v>57303</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,36 +2852,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2874,13 +2885,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701354</v>
+        <v>701365</v>
       </c>
       <c r="R20" t="n">
-        <v>6359384</v>
+        <v>6359342</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2920,11 +2931,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2941,10 +2947,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118022367</v>
+        <v>118022407</v>
       </c>
       <c r="B21" t="n">
-        <v>108703</v>
+        <v>102044</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2953,41 +2959,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701152</v>
+        <v>701353</v>
       </c>
       <c r="R21" t="n">
-        <v>6359301</v>
+        <v>6359389</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3017,6 +3037,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>30 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,7 +3073,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118022406</v>
+        <v>118022403</v>
       </c>
       <c r="B22" t="n">
         <v>102044</v>
@@ -3083,7 +3108,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3102,13 +3127,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701354</v>
+        <v>701356</v>
       </c>
       <c r="R22" t="n">
-        <v>6359384</v>
+        <v>6359377</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3142,7 +3167,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>3 småskott varav 1ex 1 m hög. Flackare strandvall.</t>
+          <t>1,9 m + 2 m höga. Sterila=angripna.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3156,7 +3181,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3174,10 +3199,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118022475</v>
+        <v>118022388</v>
       </c>
       <c r="B23" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3190,56 +3215,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701355</v>
+        <v>701297</v>
       </c>
       <c r="R23" t="n">
-        <v>6359352</v>
+        <v>6359321</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3277,13 +3283,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3301,7 +3306,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118022391</v>
+        <v>118022395</v>
       </c>
       <c r="B24" t="n">
         <v>102044</v>
@@ -3355,10 +3360,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701336</v>
+        <v>701356</v>
       </c>
       <c r="R24" t="n">
-        <v>6359312</v>
+        <v>6359344</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3409,7 +3414,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3427,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118022474</v>
+        <v>118022346</v>
       </c>
       <c r="B25" t="n">
-        <v>42953</v>
+        <v>102044</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3439,25 +3444,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3467,17 +3472,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701336</v>
+        <v>701238</v>
       </c>
       <c r="R25" t="n">
-        <v>6359312</v>
+        <v>6359528</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3524,19 +3524,23 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1,1 m hög.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3554,10 +3558,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118022538</v>
+        <v>118022394</v>
       </c>
       <c r="B26" t="n">
-        <v>57990</v>
+        <v>108703</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3570,43 +3574,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701298</v>
+        <v>701358</v>
       </c>
       <c r="R26" t="n">
-        <v>6359287</v>
+        <v>6359325</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3649,6 +3644,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalktallskog med mycket enbuskar.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3665,7 +3665,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118022369</v>
+        <v>118022367</v>
       </c>
       <c r="B27" t="n">
         <v>108703</v>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701176</v>
+        <v>701152</v>
       </c>
       <c r="R27" t="n">
-        <v>6359312</v>
+        <v>6359301</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118022396</v>
+        <v>118022391</v>
       </c>
       <c r="B28" t="n">
         <v>102044</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701356</v>
+        <v>701336</v>
       </c>
       <c r="R28" t="n">
-        <v>6359346</v>
+        <v>6359312</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>80 cm hög.</t>
+          <t>1 m hög.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118022403</v>
+        <v>118022406</v>
       </c>
       <c r="B29" t="n">
         <v>102044</v>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701356</v>
+        <v>701354</v>
       </c>
       <c r="R29" t="n">
-        <v>6359377</v>
+        <v>6359384</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1,9 m + 2 m höga. Sterila=angripna.</t>
+          <t>3 småskott varav 1ex 1 m hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118022402</v>
+        <v>118022376</v>
       </c>
       <c r="B30" t="n">
         <v>102044</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4078,13 +4078,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701357</v>
+        <v>701237</v>
       </c>
       <c r="R30" t="n">
-        <v>6359376</v>
+        <v>6359313</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3,5 m (steril, angripen) + 4 m höga (fertil).</t>
+          <t>1m hög; på åsrygg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118022538</v>
+        <v>118022348</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>102046</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>6037533</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701298</v>
+        <v>701238</v>
       </c>
       <c r="R2" t="n">
-        <v>6359287</v>
+        <v>6359519</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,6 +767,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1,2 m hög.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,6 +780,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalktallskog med mycket enbuskar.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118022427</v>
+        <v>118022473</v>
       </c>
       <c r="B3" t="n">
-        <v>100097</v>
+        <v>42953</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +813,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>101242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701333</v>
+        <v>701221</v>
       </c>
       <c r="R3" t="n">
-        <v>6359501</v>
+        <v>6359309</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,12 +904,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -893,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118022475</v>
+        <v>118022367</v>
       </c>
       <c r="B4" t="n">
-        <v>42953</v>
+        <v>108705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,53 +944,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701355</v>
+        <v>701152</v>
       </c>
       <c r="R4" t="n">
-        <v>6359352</v>
+        <v>6359301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,13 +1012,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1020,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118022348</v>
+        <v>118022384</v>
       </c>
       <c r="B5" t="n">
-        <v>102044</v>
+        <v>108705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,55 +1047,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701238</v>
+        <v>701278</v>
       </c>
       <c r="R5" t="n">
-        <v>6359519</v>
+        <v>6359306</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,11 +1111,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1,2 m hög.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118022408</v>
+        <v>118022395</v>
       </c>
       <c r="B6" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,13 +1196,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701358</v>
+        <v>701356</v>
       </c>
       <c r="R6" t="n">
-        <v>6359389</v>
+        <v>6359344</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>40 cm hög. Flackare strandvall.</t>
+          <t>1 m hög.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,7 +1250,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1272,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118022399</v>
+        <v>118022406</v>
       </c>
       <c r="B7" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,7 +1303,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1326,13 +1322,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701351</v>
+        <v>701354</v>
       </c>
       <c r="R7" t="n">
-        <v>6359353</v>
+        <v>6359384</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,7 +1362,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mindre plantor.</t>
+          <t>3 småskott varav 1ex 1 m hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,7 +1376,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1398,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118022405</v>
+        <v>118022398</v>
       </c>
       <c r="B8" t="n">
-        <v>106765</v>
+        <v>102046</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,30 +1406,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220079</v>
+        <v>6037533</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1452,13 +1448,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701354</v>
+        <v>701355</v>
       </c>
       <c r="R8" t="n">
-        <v>6359384</v>
+        <v>6359352</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1490,6 +1486,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>60 cm hög.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1501,7 +1502,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1522,7 +1523,7 @@
         <v>118022369</v>
       </c>
       <c r="B9" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1626,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118022404</v>
+        <v>118022403</v>
       </c>
       <c r="B10" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,7 +1662,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1680,7 +1681,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701354</v>
+        <v>701356</v>
       </c>
       <c r="R10" t="n">
         <v>6359377</v>
@@ -1720,7 +1721,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>4-5 m höga, spensliga, sterila =angripna.</t>
+          <t>1,9 m + 2 m höga. Sterila=angripna.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118022371</v>
+        <v>118022427</v>
       </c>
       <c r="B11" t="n">
-        <v>106109</v>
+        <v>100099</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,25 +1765,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1792,13 +1793,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701190</v>
+        <v>701333</v>
       </c>
       <c r="R11" t="n">
-        <v>6359305</v>
+        <v>6359501</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1830,11 +1831,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tycks spridd l'ängs rävstig.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1846,7 +1842,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar; gammalt grustag i strandvall ev.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1864,10 +1860,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118022396</v>
+        <v>118022399</v>
       </c>
       <c r="B12" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1918,10 +1914,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701356</v>
+        <v>701351</v>
       </c>
       <c r="R12" t="n">
-        <v>6359346</v>
+        <v>6359353</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1958,7 +1954,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>80 cm hög.</t>
+          <t>Mindre plantor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,10 +1986,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118022402</v>
+        <v>118022538</v>
       </c>
       <c r="B13" t="n">
-        <v>102044</v>
+        <v>57991</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,40 +1998,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2044,13 +2035,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701357</v>
+        <v>701298</v>
       </c>
       <c r="R13" t="n">
-        <v>6359376</v>
+        <v>6359287</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2082,11 +2073,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3,5 m (steril, angripen) + 4 m höga (fertil).</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2095,11 +2081,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2116,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118022401</v>
+        <v>118022371</v>
       </c>
       <c r="B14" t="n">
-        <v>102044</v>
+        <v>106111</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,55 +2109,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6037533</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701357</v>
+        <v>701190</v>
       </c>
       <c r="R14" t="n">
-        <v>6359355</v>
+        <v>6359305</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,7 +2177,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 3 m hög, stam 5 cm i diameter, fertil, död stam 4 cm med skott.</t>
+          <t>Tycks spridd l'ängs rävstig.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,7 +2191,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar; gammalt grustag i strandvall ev.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2242,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118022474</v>
+        <v>118022407</v>
       </c>
       <c r="B15" t="n">
-        <v>42953</v>
+        <v>102046</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2254,25 +2221,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2282,17 +2249,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2301,13 +2263,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701336</v>
+        <v>701353</v>
       </c>
       <c r="R15" t="n">
-        <v>6359312</v>
+        <v>6359389</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2339,19 +2301,23 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>30 cm hög. Flackare strandvall.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2369,10 +2335,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118022473</v>
+        <v>118022394</v>
       </c>
       <c r="B16" t="n">
-        <v>42953</v>
+        <v>108705</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2385,56 +2351,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701221</v>
+        <v>701358</v>
       </c>
       <c r="R16" t="n">
-        <v>6359309</v>
+        <v>6359325</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2472,13 +2419,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2496,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118022366</v>
+        <v>118022346</v>
       </c>
       <c r="B17" t="n">
-        <v>108703</v>
+        <v>102046</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2508,41 +2454,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701112</v>
+        <v>701238</v>
       </c>
       <c r="R17" t="n">
-        <v>6359275</v>
+        <v>6359528</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2572,6 +2532,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1,1 m hög.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,10 +2568,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118022398</v>
+        <v>118022402</v>
       </c>
       <c r="B18" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2638,7 +2603,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2648,7 +2613,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2657,10 +2622,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701355</v>
+        <v>701357</v>
       </c>
       <c r="R18" t="n">
-        <v>6359352</v>
+        <v>6359376</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2697,7 +2662,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>60 cm hög.</t>
+          <t>3,5 m (steril, angripen) + 4 m höga (fertil).</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,7 +2676,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2729,10 +2694,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118022384</v>
+        <v>118022401</v>
       </c>
       <c r="B19" t="n">
-        <v>108703</v>
+        <v>102046</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2741,41 +2706,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701278</v>
+        <v>701357</v>
       </c>
       <c r="R19" t="n">
-        <v>6359306</v>
+        <v>6359355</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2807,6 +2786,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ca 3 m hög, stam 5 cm i diameter, fertil, död stam 4 cm med skott.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2818,7 +2802,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2836,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118022540</v>
+        <v>118022405</v>
       </c>
       <c r="B20" t="n">
-        <v>57303</v>
+        <v>106767</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2852,31 +2836,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2885,13 +2874,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701365</v>
+        <v>701354</v>
       </c>
       <c r="R20" t="n">
-        <v>6359342</v>
+        <v>6359384</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2931,6 +2920,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalktallskog med mycket enbuskar.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2947,10 +2941,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118022407</v>
+        <v>118022475</v>
       </c>
       <c r="B21" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2959,25 +2953,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2987,12 +2981,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3001,13 +3000,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701353</v>
+        <v>701355</v>
       </c>
       <c r="R21" t="n">
-        <v>6359389</v>
+        <v>6359352</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3039,23 +3038,19 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>30 cm hög. Flackare strandvall.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3073,10 +3068,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118022403</v>
+        <v>118022404</v>
       </c>
       <c r="B22" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3108,7 +3103,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3127,7 +3122,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701356</v>
+        <v>701354</v>
       </c>
       <c r="R22" t="n">
         <v>6359377</v>
@@ -3167,7 +3162,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1,9 m + 2 m höga. Sterila=angripna.</t>
+          <t>4-5 m höga, spensliga, sterila =angripna.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3199,10 +3194,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118022388</v>
+        <v>118022366</v>
       </c>
       <c r="B23" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3239,10 +3234,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701297</v>
+        <v>701112</v>
       </c>
       <c r="R23" t="n">
-        <v>6359321</v>
+        <v>6359275</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3306,10 +3301,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118022395</v>
+        <v>118022388</v>
       </c>
       <c r="B24" t="n">
-        <v>102044</v>
+        <v>108705</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,55 +3313,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701356</v>
+        <v>701297</v>
       </c>
       <c r="R24" t="n">
-        <v>6359344</v>
+        <v>6359321</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3398,11 +3379,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 m hög.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3414,7 +3390,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3432,10 +3408,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118022346</v>
+        <v>118022396</v>
       </c>
       <c r="B25" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3486,10 +3462,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>701238</v>
+        <v>701356</v>
       </c>
       <c r="R25" t="n">
-        <v>6359528</v>
+        <v>6359346</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3526,7 +3502,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1,1 m hög.</t>
+          <t>80 cm hög.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3540,7 +3516,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3558,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118022394</v>
+        <v>118022408</v>
       </c>
       <c r="B26" t="n">
-        <v>108703</v>
+        <v>102046</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3570,28 +3546,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
@@ -3601,7 +3591,7 @@
         <v>701358</v>
       </c>
       <c r="R26" t="n">
-        <v>6359325</v>
+        <v>6359389</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3634,6 +3624,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>40 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3665,10 +3660,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118022367</v>
+        <v>118022391</v>
       </c>
       <c r="B27" t="n">
-        <v>108703</v>
+        <v>102046</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3677,41 +3672,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701152</v>
+        <v>701336</v>
       </c>
       <c r="R27" t="n">
-        <v>6359301</v>
+        <v>6359312</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3741,6 +3750,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 m hög.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3772,10 +3786,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118022391</v>
+        <v>118022376</v>
       </c>
       <c r="B28" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3826,13 +3840,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701336</v>
+        <v>701237</v>
       </c>
       <c r="R28" t="n">
-        <v>6359312</v>
+        <v>6359313</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3866,7 +3880,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1 m hög.</t>
+          <t>1m hög; på åsrygg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3898,10 +3912,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118022406</v>
+        <v>118022540</v>
       </c>
       <c r="B29" t="n">
-        <v>102044</v>
+        <v>57304</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3910,40 +3924,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6037533</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3952,13 +3961,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701354</v>
+        <v>701365</v>
       </c>
       <c r="R29" t="n">
-        <v>6359384</v>
+        <v>6359342</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3990,11 +3999,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>3 småskott varav 1ex 1 m hög. Flackare strandvall.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4003,11 +4007,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4024,10 +4023,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118022376</v>
+        <v>118022474</v>
       </c>
       <c r="B30" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4036,25 +4035,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4064,12 +4063,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4078,13 +4082,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701237</v>
+        <v>701336</v>
       </c>
       <c r="R30" t="n">
-        <v>6359313</v>
+        <v>6359312</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4116,23 +4120,19 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1m hög; på åsrygg.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -3660,10 +3660,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118022391</v>
+        <v>118022540</v>
       </c>
       <c r="B27" t="n">
-        <v>102046</v>
+        <v>57304</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6037533</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3698,14 +3698,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3714,13 +3709,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701336</v>
+        <v>701365</v>
       </c>
       <c r="R27" t="n">
-        <v>6359312</v>
+        <v>6359342</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3752,11 +3747,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 m hög.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3765,11 +3755,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3786,10 +3771,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118022376</v>
+        <v>118022474</v>
       </c>
       <c r="B28" t="n">
-        <v>102046</v>
+        <v>42953</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3798,25 +3783,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3826,12 +3811,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3840,13 +3830,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>701237</v>
+        <v>701336</v>
       </c>
       <c r="R28" t="n">
-        <v>6359313</v>
+        <v>6359312</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3878,23 +3868,19 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>1m hög; på åsrygg.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3912,10 +3898,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118022540</v>
+        <v>118022391</v>
       </c>
       <c r="B29" t="n">
-        <v>57304</v>
+        <v>102046</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3924,25 +3910,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6037533</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3950,9 +3936,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3961,13 +3952,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701365</v>
+        <v>701336</v>
       </c>
       <c r="R29" t="n">
-        <v>6359342</v>
+        <v>6359312</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3999,6 +3990,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 m hög.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4007,6 +4003,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalktallskog med mycket enbuskar.</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4023,10 +4024,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118022474</v>
+        <v>118022376</v>
       </c>
       <c r="B30" t="n">
-        <v>42953</v>
+        <v>102046</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4035,25 +4036,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4063,17 +4064,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4082,13 +4078,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>701336</v>
+        <v>701237</v>
       </c>
       <c r="R30" t="n">
-        <v>6359312</v>
+        <v>6359313</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4120,19 +4116,23 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1m hög; på åsrygg.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4148,6 +4148,256 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121391837</v>
+      </c>
+      <c r="B31" t="n">
+        <v>102286</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>701238</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6359523</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>I-Got-1586</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bengt Carlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121391839</v>
+      </c>
+      <c r="B32" t="n">
+        <v>102286</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, punkt 84 m 265 m SO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>701368</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6359350</v>
+      </c>
+      <c r="S32" t="n">
+        <v>57</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>I-Got-1584</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>19 träd/plantor med koordinater 1652946 6359125 (1 m), 1652962 6359166 (mindre plantor), 1652964 6359202 (0,3 m), 1652965 6359190 (4–5 m), 1652965 6359197 (1 m + småskott), 1652966 6359165 (0,6 m), 1652967 6359157 (1 m), 1652967 6359159 (0,8 m), 1652967 6359190 (1,9 m + 2 m), 1652968 6359168 (3 m), 1652968 6359189 (3, 5 m + 4 m), 1652969 6359202 (0,4 m)</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bengt Carlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4153,7 +4153,7 @@
         <v>121391837</v>
       </c>
       <c r="B31" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>121391839</v>
       </c>
       <c r="B32" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4153,7 +4153,7 @@
         <v>121391837</v>
       </c>
       <c r="B31" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>121391839</v>
       </c>
       <c r="B32" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4153,7 +4153,7 @@
         <v>121391837</v>
       </c>
       <c r="B31" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>121391839</v>
       </c>
       <c r="B32" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701368</v>
+        <v>701354</v>
       </c>
       <c r="R32" t="n">
-        <v>6359350</v>
+        <v>6359351</v>
       </c>
       <c r="S32" t="n">
         <v>57</v>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4150,10 +4150,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121391837</v>
+        <v>121391839</v>
       </c>
       <c r="B31" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4195,17 +4195,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 265 m SO, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>701238</v>
+        <v>701354</v>
       </c>
       <c r="R31" t="n">
-        <v>6359523</v>
+        <v>6359351</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>I-Got-1586</t>
+          <t>I-Got-1584</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
+          <t>19 träd/plantor med koordinater 1652946 6359125 (1 m), 1652962 6359166 (mindre plantor), 1652964 6359202 (0,3 m), 1652965 6359190 (4–5 m), 1652965 6359197 (1 m + småskott), 1652966 6359165 (0,6 m), 1652967 6359157 (1 m), 1652967 6359159 (0,8 m), 1652967 6359190 (1,9 m + 2 m), 1652968 6359168 (3 m), 1652968 6359189 (3, 5 m + 4 m), 1652969 6359202 (0,4 m)</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4275,10 +4275,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121391839</v>
+        <v>121391837</v>
       </c>
       <c r="B32" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 265 m SO, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>701354</v>
+        <v>701238</v>
       </c>
       <c r="R32" t="n">
-        <v>6359351</v>
+        <v>6359523</v>
       </c>
       <c r="S32" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>I-Got-1584</t>
+          <t>I-Got-1586</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>19 träd/plantor med koordinater 1652946 6359125 (1 m), 1652962 6359166 (mindre plantor), 1652964 6359202 (0,3 m), 1652965 6359190 (4–5 m), 1652965 6359197 (1 m + småskott), 1652966 6359165 (0,6 m), 1652967 6359157 (1 m), 1652967 6359159 (0,8 m), 1652967 6359190 (1,9 m + 2 m), 1652968 6359168 (3 m), 1652968 6359189 (3, 5 m + 4 m), 1652969 6359202 (0,4 m)</t>
+          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4153,7 +4153,7 @@
         <v>121391839</v>
       </c>
       <c r="B31" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>121391837</v>
       </c>
       <c r="B32" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4153,7 +4153,7 @@
         <v>121391839</v>
       </c>
       <c r="B31" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>121391837</v>
       </c>
       <c r="B32" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -2246,11 +2246,11 @@
         <v>118022540</v>
       </c>
       <c r="B15" t="n">
-        <v>57306</v>
+        <v>57497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -2246,7 +2246,7 @@
         <v>118022540</v>
       </c>
       <c r="B15" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4153,11 +4153,11 @@
         <v>121391839</v>
       </c>
       <c r="B31" t="n">
-        <v>102328</v>
+        <v>102612</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4278,11 +4278,11 @@
         <v>121391837</v>
       </c>
       <c r="B32" t="n">
-        <v>102328</v>
+        <v>102612</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -2246,7 +2246,7 @@
         <v>118022540</v>
       </c>
       <c r="B15" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>121391839</v>
       </c>
       <c r="B31" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>121391837</v>
       </c>
       <c r="B32" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -2246,7 +2246,7 @@
         <v>118022540</v>
       </c>
       <c r="B15" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>121391839</v>
       </c>
       <c r="B31" t="n">
-        <v>102630</v>
+        <v>102632</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>121391837</v>
       </c>
       <c r="B32" t="n">
-        <v>102630</v>
+        <v>102632</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4153,7 +4153,7 @@
         <v>121391839</v>
       </c>
       <c r="B31" t="n">
-        <v>102632</v>
+        <v>102207</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>121391837</v>
       </c>
       <c r="B32" t="n">
-        <v>102632</v>
+        <v>102207</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4398,6 +4398,595 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126382861</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58371</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>701315</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6359368</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Fanns här även 2024.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126382775</v>
+      </c>
+      <c r="B34" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lojsta  Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>701315</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6359368</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Vid snitslad tall.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126382899</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58371</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>701064</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6359334</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126382818</v>
+      </c>
+      <c r="B36" t="n">
+        <v>102485</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lojsta  Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>701315</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6359368</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1,65 cm hög, stam 1 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126382722</v>
+      </c>
+      <c r="B37" t="n">
+        <v>102485</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>701310</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6359412</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>4 m hög, en grövre stam ca 4 cm i diameter plus tre smala stammar. Bladen är angripna av spinn.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4403,7 +4403,7 @@
         <v>126382861</v>
       </c>
       <c r="B33" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>126382775</v>
       </c>
       <c r="B34" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>126382899</v>
       </c>
       <c r="B35" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>126382818</v>
       </c>
       <c r="B36" t="n">
-        <v>102485</v>
+        <v>102494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>126382722</v>
       </c>
       <c r="B37" t="n">
-        <v>102485</v>
+        <v>102494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4874,10 +4874,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126382722</v>
+        <v>133906278</v>
       </c>
       <c r="B37" t="n">
-        <v>102494</v>
+        <v>103328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4907,17 +4907,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, Gtl</t>
+          <t>Lojsta, Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -4927,7 +4924,7 @@
         <v>6359412</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4951,17 +4948,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>4 m hög, en grövre stam ca 4 cm i diameter plus tre smala stammar. Bladen är angripna av spinn.</t>
+          <t>Toppen av. Skador på stammen. Kvarstående 5 m utanför yta för naturhänsyn. Avverkade träd runt omkring, varvid stam och topp har skadats på den tidigare registrereade garderönnen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4970,22 +4967,354 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133906322</v>
+      </c>
+      <c r="B38" t="n">
+        <v>103328</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lojsta, Båtels 1:12., Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>701286</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6359368</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>0,5 m hög</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133906277</v>
+      </c>
+      <c r="B39" t="n">
+        <v>103328</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lojsta, Båtels 1:12., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>701302</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6359396</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Inom det sparade skiftet. 1,4 m hög. En småplanta 2 m söder om.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133906279</v>
+      </c>
+      <c r="B40" t="n">
+        <v>103328</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lojsta, Båtels 1:12., Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>701333</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6359426</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Kvarstående på strandvall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4877,7 +4877,7 @@
         <v>133906278</v>
       </c>
       <c r="B37" t="n">
-        <v>103328</v>
+        <v>103330</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>133906322</v>
       </c>
       <c r="B38" t="n">
-        <v>103328</v>
+        <v>103330</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>133906277</v>
       </c>
       <c r="B39" t="n">
-        <v>103328</v>
+        <v>103330</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>133906279</v>
       </c>
       <c r="B40" t="n">
-        <v>103328</v>
+        <v>103330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4877,7 +4877,7 @@
         <v>133906278</v>
       </c>
       <c r="B37" t="n">
-        <v>103330</v>
+        <v>103358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>133906322</v>
       </c>
       <c r="B38" t="n">
-        <v>103330</v>
+        <v>103358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>133906277</v>
       </c>
       <c r="B39" t="n">
-        <v>103330</v>
+        <v>103358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>133906279</v>
       </c>
       <c r="B40" t="n">
-        <v>103330</v>
+        <v>103358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 21467-2024 artfynd.xlsx
+++ b/artfynd/A 21467-2024 artfynd.xlsx
@@ -4877,7 +4877,7 @@
         <v>133906278</v>
       </c>
       <c r="B37" t="n">
-        <v>103358</v>
+        <v>103368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>133906322</v>
       </c>
       <c r="B38" t="n">
-        <v>103358</v>
+        <v>103368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>133906277</v>
       </c>
       <c r="B39" t="n">
-        <v>103358</v>
+        <v>103368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>133906279</v>
       </c>
       <c r="B40" t="n">
-        <v>103358</v>
+        <v>103368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
